--- a/config/tutorial_RC.xlsx
+++ b/config/tutorial_RC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\q516645\Desktop\Github_ext\TherMOS\config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schir\OneDrive\Studium\34_Github\TherMOS\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C556878-79B8-4033-8E2B-9C7838B47342}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BDF8ED0-C64B-4A00-BFE4-ABF724044424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1470" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="3" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
   </bookViews>
   <sheets>
     <sheet name="readme" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="260">
   <si>
     <t>#</t>
   </si>
@@ -798,6 +798,91 @@
   </si>
   <si>
     <t>Emax</t>
+  </si>
+  <si>
+    <t>BasisFunction</t>
+  </si>
+  <si>
+    <t>gpr</t>
+  </si>
+  <si>
+    <t>Explicit basis in the GPR model:
+1) Constant
+2) Linear
+3) Quadratic</t>
+  </si>
+  <si>
+    <t>basis</t>
+  </si>
+  <si>
+    <t>Form of the covariance function, specified as one of the following:
+1) Exponential
+2) Squareexponential</t>
+  </si>
+  <si>
+    <t>IterationLimit</t>
+  </si>
+  <si>
+    <t>Maximum number of block coordinate descent method ("bcd") iterations.</t>
+  </si>
+  <si>
+    <t>Method</t>
+  </si>
+  <si>
+    <t>en</t>
+  </si>
+  <si>
+    <t>Ensemble aggregation method:
+1) LSBoost
+2) Bag</t>
+  </si>
+  <si>
+    <t>method</t>
+  </si>
+  <si>
+    <t>LearningCycles</t>
+  </si>
+  <si>
+    <t>Number of ensemble learning cycles</t>
+  </si>
+  <si>
+    <t>cycle</t>
+  </si>
+  <si>
+    <t>nn</t>
+  </si>
+  <si>
+    <t>Maximum number of training iterations</t>
+  </si>
+  <si>
+    <t>NumberLayers</t>
+  </si>
+  <si>
+    <t>Number of fully connected layers in the network.</t>
+  </si>
+  <si>
+    <t>layer</t>
+  </si>
+  <si>
+    <t>NumberNeurons</t>
+  </si>
+  <si>
+    <t>Number of nodes per fully connected layer.</t>
+  </si>
+  <si>
+    <t>nodes</t>
+  </si>
+  <si>
+    <t>Activation</t>
+  </si>
+  <si>
+    <t>Activation functions for the fully connected layers of the neural network model:
+1) relu
+2) tanh
+3) sigmoid</t>
+  </si>
+  <si>
+    <t>act</t>
   </si>
 </sst>
 </file>
@@ -1372,7 +1457,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1388,9 +1473,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 – 2022">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1428,7 +1513,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 – 2022">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1534,7 +1619,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 – 2022">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1685,17 +1770,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA655AC4-52E1-45C0-83AC-CC64B56C05A9}">
   <dimension ref="A1:L18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="45.7109375" customWidth="1"/>
-    <col min="5" max="6" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="51.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="45.6640625" customWidth="1"/>
+    <col min="5" max="6" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="51.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>4</v>
       </c>
@@ -1703,7 +1788,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
@@ -1711,7 +1796,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
@@ -1719,7 +1804,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>7</v>
       </c>
@@ -1727,8 +1812,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="13" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>0</v>
       </c>
@@ -1753,7 +1838,7 @@
       <c r="K13" s="51"/>
       <c r="L13" s="52"/>
     </row>
-    <row r="14" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>1</v>
       </c>
@@ -1782,7 +1867,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>2</v>
       </c>
@@ -1794,7 +1879,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>3</v>
       </c>
@@ -1806,7 +1891,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>4</v>
       </c>
@@ -1818,7 +1903,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>5</v>
       </c>
@@ -1845,15 +1930,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CAB857B-5D2E-4BE1-B462-B4B5EEAA4370}">
   <dimension ref="A1:G30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" style="37" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" style="37" customWidth="1"/>
     <col min="3" max="3" width="48" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.28515625" customWidth="1"/>
+    <col min="4" max="5" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="32" t="s">
         <v>1</v>
       </c>
@@ -1876,7 +1961,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="75.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="58.2" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>89</v>
       </c>
@@ -1899,7 +1984,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>90</v>
       </c>
@@ -1922,7 +2007,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>91</v>
       </c>
@@ -1945,7 +2030,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>163</v>
       </c>
@@ -1968,7 +2053,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
         <v>164</v>
       </c>
@@ -1991,7 +2076,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
         <v>92</v>
       </c>
@@ -2014,7 +2099,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="13"/>
       <c r="B8" s="26"/>
       <c r="C8" s="5"/>
@@ -2023,7 +2108,7 @@
       <c r="F8" s="6"/>
       <c r="G8" s="29"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="13"/>
       <c r="B9" s="26"/>
       <c r="C9" s="5"/>
@@ -2032,7 +2117,7 @@
       <c r="F9" s="6"/>
       <c r="G9" s="29"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="13"/>
       <c r="B10" s="26"/>
       <c r="C10" s="5"/>
@@ -2041,7 +2126,7 @@
       <c r="F10" s="6"/>
       <c r="G10" s="29"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="13"/>
       <c r="B11" s="26"/>
       <c r="C11" s="5"/>
@@ -2050,7 +2135,7 @@
       <c r="F11" s="6"/>
       <c r="G11" s="29"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="13"/>
       <c r="B12" s="26"/>
       <c r="C12" s="5"/>
@@ -2059,7 +2144,7 @@
       <c r="F12" s="6"/>
       <c r="G12" s="29"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="13"/>
       <c r="B13" s="26"/>
       <c r="C13" s="5"/>
@@ -2068,7 +2153,7 @@
       <c r="F13" s="6"/>
       <c r="G13" s="29"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>
       <c r="B14" s="26"/>
       <c r="C14" s="5"/>
@@ -2077,7 +2162,7 @@
       <c r="F14" s="6"/>
       <c r="G14" s="29"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>
       <c r="B15" s="26"/>
       <c r="C15" s="5"/>
@@ -2086,7 +2171,7 @@
       <c r="F15" s="6"/>
       <c r="G15" s="29"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="13"/>
       <c r="B16" s="26"/>
       <c r="C16" s="5"/>
@@ -2095,7 +2180,7 @@
       <c r="F16" s="6"/>
       <c r="G16" s="29"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="13"/>
       <c r="B17" s="26"/>
       <c r="C17" s="5"/>
@@ -2104,7 +2189,7 @@
       <c r="F17" s="6"/>
       <c r="G17" s="29"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="13"/>
       <c r="B18" s="26"/>
       <c r="C18" s="5"/>
@@ -2113,7 +2198,7 @@
       <c r="F18" s="6"/>
       <c r="G18" s="29"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="13"/>
       <c r="B19" s="26"/>
       <c r="C19" s="5"/>
@@ -2122,7 +2207,7 @@
       <c r="F19" s="6"/>
       <c r="G19" s="29"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="13"/>
       <c r="B20" s="26"/>
       <c r="C20" s="5"/>
@@ -2131,7 +2216,7 @@
       <c r="F20" s="6"/>
       <c r="G20" s="29"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="13"/>
       <c r="B21" s="26"/>
       <c r="C21" s="5"/>
@@ -2140,7 +2225,7 @@
       <c r="F21" s="6"/>
       <c r="G21" s="29"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="13"/>
       <c r="B22" s="26"/>
       <c r="C22" s="5"/>
@@ -2149,7 +2234,7 @@
       <c r="F22" s="6"/>
       <c r="G22" s="29"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="13"/>
       <c r="B23" s="26"/>
       <c r="C23" s="5"/>
@@ -2158,7 +2243,7 @@
       <c r="F23" s="6"/>
       <c r="G23" s="29"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="13"/>
       <c r="B24" s="26"/>
       <c r="C24" s="5"/>
@@ -2167,7 +2252,7 @@
       <c r="F24" s="6"/>
       <c r="G24" s="29"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="13"/>
       <c r="B25" s="26"/>
       <c r="C25" s="5"/>
@@ -2176,7 +2261,7 @@
       <c r="F25" s="6"/>
       <c r="G25" s="29"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="13"/>
       <c r="B26" s="26"/>
       <c r="C26" s="5"/>
@@ -2185,7 +2270,7 @@
       <c r="F26" s="6"/>
       <c r="G26" s="29"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="13"/>
       <c r="B27" s="26"/>
       <c r="C27" s="5"/>
@@ -2194,7 +2279,7 @@
       <c r="F27" s="6"/>
       <c r="G27" s="29"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="13"/>
       <c r="B28" s="26"/>
       <c r="C28" s="5"/>
@@ -2203,7 +2288,7 @@
       <c r="F28" s="6"/>
       <c r="G28" s="29"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="13"/>
       <c r="B29" s="26"/>
       <c r="C29" s="5"/>
@@ -2212,7 +2297,7 @@
       <c r="F29" s="6"/>
       <c r="G29" s="29"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="13"/>
       <c r="B30" s="26"/>
       <c r="C30" s="5"/>
@@ -2247,15 +2332,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86190CFD-1D2B-4FE4-A04E-A3C453840C86}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" customWidth="1"/>
     <col min="3" max="3" width="48" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.28515625" customWidth="1"/>
+    <col min="4" max="5" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="32" t="s">
         <v>1</v>
       </c>
@@ -2278,7 +2363,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="45.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="43.8" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>93</v>
       </c>
@@ -2301,7 +2386,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>94</v>
       </c>
@@ -2324,7 +2409,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>97</v>
       </c>
@@ -2347,7 +2432,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>109</v>
       </c>
@@ -2370,7 +2455,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
         <v>110</v>
       </c>
@@ -2393,7 +2478,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
         <v>111</v>
       </c>
@@ -2416,7 +2501,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
         <v>112</v>
       </c>
@@ -2439,7 +2524,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
         <v>113</v>
       </c>
@@ -2462,7 +2547,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
         <v>114</v>
       </c>
@@ -2485,7 +2570,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="13"/>
       <c r="B11" s="25"/>
       <c r="C11" s="5"/>
@@ -2494,7 +2579,7 @@
       <c r="F11" s="6"/>
       <c r="G11" s="29"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="13"/>
       <c r="B12" s="25"/>
       <c r="C12" s="5"/>
@@ -2503,7 +2588,7 @@
       <c r="F12" s="6"/>
       <c r="G12" s="29"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="13"/>
       <c r="B13" s="25"/>
       <c r="C13" s="5"/>
@@ -2512,7 +2597,7 @@
       <c r="F13" s="6"/>
       <c r="G13" s="29"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>
       <c r="B14" s="25"/>
       <c r="C14" s="5"/>
@@ -2521,7 +2606,7 @@
       <c r="F14" s="6"/>
       <c r="G14" s="29"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>
       <c r="B15" s="25"/>
       <c r="C15" s="5"/>
@@ -2530,7 +2615,7 @@
       <c r="F15" s="6"/>
       <c r="G15" s="29"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="13"/>
       <c r="B16" s="25"/>
       <c r="C16" s="5"/>
@@ -2539,7 +2624,7 @@
       <c r="F16" s="6"/>
       <c r="G16" s="29"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="13"/>
       <c r="B17" s="25"/>
       <c r="C17" s="5"/>
@@ -2548,7 +2633,7 @@
       <c r="F17" s="6"/>
       <c r="G17" s="29"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="13"/>
       <c r="B18" s="25"/>
       <c r="C18" s="5"/>
@@ -2557,7 +2642,7 @@
       <c r="F18" s="6"/>
       <c r="G18" s="29"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="13"/>
       <c r="B19" s="25"/>
       <c r="C19" s="5"/>
@@ -2566,7 +2651,7 @@
       <c r="F19" s="6"/>
       <c r="G19" s="29"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="13"/>
       <c r="B20" s="25"/>
       <c r="C20" s="5"/>
@@ -2575,7 +2660,7 @@
       <c r="F20" s="6"/>
       <c r="G20" s="29"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="13"/>
       <c r="B21" s="25"/>
       <c r="C21" s="5"/>
@@ -2584,7 +2669,7 @@
       <c r="F21" s="6"/>
       <c r="G21" s="29"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="13"/>
       <c r="B22" s="25"/>
       <c r="C22" s="5"/>
@@ -2593,7 +2678,7 @@
       <c r="F22" s="6"/>
       <c r="G22" s="29"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="13"/>
       <c r="B23" s="25"/>
       <c r="C23" s="5"/>
@@ -2602,7 +2687,7 @@
       <c r="F23" s="6"/>
       <c r="G23" s="29"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="13"/>
       <c r="B24" s="25"/>
       <c r="C24" s="5"/>
@@ -2611,7 +2696,7 @@
       <c r="F24" s="6"/>
       <c r="G24" s="29"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="13"/>
       <c r="B25" s="25"/>
       <c r="C25" s="5"/>
@@ -2620,7 +2705,7 @@
       <c r="F25" s="6"/>
       <c r="G25" s="29"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="13"/>
       <c r="B26" s="25"/>
       <c r="C26" s="5"/>
@@ -2650,17 +2735,17 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{799FBFCB-8244-4B83-8CC9-EBD2890613E5}">
-  <dimension ref="A1:G43"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G53"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" style="37" customWidth="1"/>
+    <col min="1" max="1" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" style="37" customWidth="1"/>
     <col min="3" max="3" width="48" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.28515625" customWidth="1"/>
-    <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="10.33203125" customWidth="1"/>
+    <col min="7" max="7" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="32" t="s">
         <v>1</v>
       </c>
@@ -2683,7 +2768,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>56</v>
       </c>
@@ -2706,7 +2791,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>57</v>
       </c>
@@ -2729,7 +2814,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>58</v>
       </c>
@@ -2752,7 +2837,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="38" t="s">
         <v>156</v>
       </c>
@@ -2775,7 +2860,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="38" t="s">
         <v>59</v>
       </c>
@@ -2798,7 +2883,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="38" t="s">
         <v>188</v>
       </c>
@@ -2821,7 +2906,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
         <v>81</v>
       </c>
@@ -2844,7 +2929,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="14" t="s">
         <v>82</v>
       </c>
@@ -2867,7 +2952,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
         <v>72</v>
       </c>
@@ -2890,7 +2975,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="14" t="s">
         <v>66</v>
       </c>
@@ -2913,7 +2998,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
         <v>71</v>
       </c>
@@ -2936,7 +3021,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
         <v>73</v>
       </c>
@@ -2959,7 +3044,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
         <v>74</v>
       </c>
@@ -2982,7 +3067,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
         <v>75</v>
       </c>
@@ -3005,7 +3090,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
         <v>76</v>
       </c>
@@ -3028,7 +3113,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="14" t="s">
         <v>168</v>
       </c>
@@ -3051,7 +3136,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="12" t="s">
         <v>79</v>
       </c>
@@ -3074,7 +3159,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="14" t="s">
         <v>80</v>
       </c>
@@ -3097,7 +3182,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="12" t="s">
         <v>169</v>
       </c>
@@ -3120,7 +3205,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A21" s="13" t="s">
         <v>172</v>
       </c>
@@ -3141,7 +3226,7 @@
       </c>
       <c r="G21" s="29"/>
     </row>
-    <row r="22" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A22" s="13" t="s">
         <v>173</v>
       </c>
@@ -3164,7 +3249,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A23" s="12" t="s">
         <v>178</v>
       </c>
@@ -3187,7 +3272,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
         <v>179</v>
       </c>
@@ -3210,7 +3295,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="14" t="s">
         <v>180</v>
       </c>
@@ -3233,7 +3318,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A26" s="12" t="s">
         <v>192</v>
       </c>
@@ -3256,7 +3341,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A27" s="13" t="s">
         <v>193</v>
       </c>
@@ -3279,7 +3364,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="14" t="s">
         <v>194</v>
       </c>
@@ -3302,7 +3387,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A29" s="12" t="s">
         <v>200</v>
       </c>
@@ -3325,7 +3410,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A30" s="13" t="s">
         <v>201</v>
       </c>
@@ -3348,7 +3433,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A31" s="13" t="s">
         <v>202</v>
       </c>
@@ -3371,7 +3456,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="13" t="s">
         <v>203</v>
       </c>
@@ -3394,7 +3479,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A33" s="13" t="s">
         <v>204</v>
       </c>
@@ -3417,7 +3502,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A34" s="13" t="s">
         <v>205</v>
       </c>
@@ -3440,7 +3525,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A35" s="13" t="s">
         <v>207</v>
       </c>
@@ -3463,7 +3548,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A36" s="13" t="s">
         <v>208</v>
       </c>
@@ -3486,7 +3571,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A37" s="38" t="s">
         <v>228</v>
       </c>
@@ -3509,7 +3594,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A38" s="38" t="s">
         <v>229</v>
       </c>
@@ -3532,7 +3617,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="14" t="s">
         <v>209</v>
       </c>
@@ -3555,54 +3640,284 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="12"/>
-      <c r="B40" s="28"/>
-      <c r="C40" s="8"/>
-      <c r="D40" s="28"/>
-      <c r="E40" s="28"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="31"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="13"/>
-      <c r="B41" s="26"/>
-      <c r="C41" s="5"/>
-      <c r="D41" s="26"/>
-      <c r="E41" s="26"/>
-      <c r="F41" s="6"/>
-      <c r="G41" s="29"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="13"/>
-      <c r="B42" s="26"/>
-      <c r="C42" s="5"/>
-      <c r="D42" s="26"/>
-      <c r="E42" s="26"/>
-      <c r="F42" s="6"/>
-      <c r="G42" s="29"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="13"/>
-      <c r="B43" s="26"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="26"/>
-      <c r="E43" s="26"/>
-      <c r="F43" s="6"/>
-      <c r="G43" s="29"/>
+    <row r="40" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A40" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="B40" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="D40" s="28" t="s">
+        <v>238</v>
+      </c>
+      <c r="E40" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="F40" s="48">
+        <v>1</v>
+      </c>
+      <c r="G40" s="31" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A41" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="B41" s="26" t="s">
+        <v>236</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="D41" s="26" t="s">
+        <v>199</v>
+      </c>
+      <c r="E41" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="F41" s="6">
+        <v>1</v>
+      </c>
+      <c r="G41" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="B42" s="27" t="s">
+        <v>236</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="D42" s="27" t="s">
+        <v>158</v>
+      </c>
+      <c r="E42" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="F42" s="10">
+        <v>100</v>
+      </c>
+      <c r="G42" s="30" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A43" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="B43" s="28" t="s">
+        <v>243</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="D43" s="28" t="s">
+        <v>245</v>
+      </c>
+      <c r="E43" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="F43" s="9">
+        <v>1</v>
+      </c>
+      <c r="G43" s="31" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="B44" s="26" t="s">
+        <v>243</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="D44" s="26" t="s">
+        <v>248</v>
+      </c>
+      <c r="E44" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="F44" s="6">
+        <v>100</v>
+      </c>
+      <c r="G44" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="B45" s="27" t="s">
+        <v>243</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="D45" s="27" t="s">
+        <v>182</v>
+      </c>
+      <c r="E45" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="F45" s="10">
+        <v>50</v>
+      </c>
+      <c r="G45" s="30" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="B46" s="28" t="s">
+        <v>249</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="D46" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="E46" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="F46" s="9">
+        <v>100</v>
+      </c>
+      <c r="G46" s="31" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="B47" s="26" t="s">
+        <v>249</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="D47" s="26" t="s">
+        <v>253</v>
+      </c>
+      <c r="E47" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="F47" s="6">
+        <v>1</v>
+      </c>
+      <c r="G47" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="B48" s="26" t="s">
+        <v>249</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="D48" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="E48" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="F48" s="6">
+        <v>50</v>
+      </c>
+      <c r="G48" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+      <c r="A49" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>249</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="D49" s="26" t="s">
+        <v>259</v>
+      </c>
+      <c r="E49" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="F49" s="9">
+        <v>1</v>
+      </c>
+      <c r="G49" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="13"/>
+      <c r="B50" s="26"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="26"/>
+      <c r="E50" s="26"/>
+      <c r="F50" s="6"/>
+      <c r="G50" s="29"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="13"/>
+      <c r="B51" s="26"/>
+      <c r="C51" s="5"/>
+      <c r="D51" s="26"/>
+      <c r="E51" s="26"/>
+      <c r="F51" s="6"/>
+      <c r="G51" s="29"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="13"/>
+      <c r="B52" s="26"/>
+      <c r="C52" s="5"/>
+      <c r="D52" s="26"/>
+      <c r="E52" s="26"/>
+      <c r="F52" s="6"/>
+      <c r="G52" s="29"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="13"/>
+      <c r="B53" s="26"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="26"/>
+      <c r="E53" s="26"/>
+      <c r="F53" s="6"/>
+      <c r="G53" s="29"/>
     </row>
   </sheetData>
   <dataValidations count="12">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F40:F43" xr:uid="{257EC82B-68B5-4F35-825F-C289285A7C45}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F50:F53" xr:uid="{A65CFE5B-68EF-4237-B683-1EC3B84E4125}">
       <formula1>"fs, fel"</formula1>
     </dataValidation>
     <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F12 F10 F18 F20 F25 F23 F38" xr:uid="{3798FD8E-D43D-4D9F-BE2C-52321394B345}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F13:F17 F21" xr:uid="{71E12662-7031-4247-910F-BB7CE1CF6CD0}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F13:F17 F21 F41 F43" xr:uid="{71E12662-7031-4247-910F-BB7CE1CF6CD0}">
       <formula1>"1, 2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F19 F26 F36" xr:uid="{37FEDC31-329E-44E8-806D-0ED1512CF102}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F19 F26 F36 F40 F49 F47" xr:uid="{37FEDC31-329E-44E8-806D-0ED1512CF102}">
       <formula1>"1, 2, 3"</formula1>
     </dataValidation>
     <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8" xr:uid="{42D8AC35-50A5-40BC-BBFA-BE08B273A500}">
@@ -3626,7 +3941,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F22" xr:uid="{47B450A3-D6D0-4908-B7DA-713464E39E93}">
       <formula1>"1, 2, 3, 4"</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F24 F29 F32 F34:F35 F37 F39" xr:uid="{4036D9AA-DD26-43F2-86CA-83C98477498F}">
+    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F24 F29 F32 F34:F35 F37 F39 F44:F46 F42 F48" xr:uid="{4036D9AA-DD26-43F2-86CA-83C98477498F}">
       <formula1>1</formula1>
     </dataValidation>
     <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F27:F28 F30:F31 F33" xr:uid="{E87A8820-6156-4E10-8AF9-95041973A5CF}">
@@ -3643,15 +3958,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{245B3F0A-B85A-4162-A12D-AC7176B54015}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" style="37" customWidth="1"/>
+    <col min="1" max="1" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" style="37" customWidth="1"/>
     <col min="3" max="3" width="48" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.28515625" customWidth="1"/>
+    <col min="4" max="5" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="32" t="s">
         <v>1</v>
       </c>
@@ -3674,7 +3989,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="75.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="72.599999999999994" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>38</v>
       </c>
@@ -3697,7 +4012,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>39</v>
       </c>
@@ -3720,7 +4035,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>40</v>
       </c>
@@ -3743,7 +4058,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>44</v>
       </c>
@@ -3766,7 +4081,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="38" t="s">
         <v>50</v>
       </c>
@@ -3789,7 +4104,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="14" t="s">
         <v>52</v>
       </c>
@@ -3812,7 +4127,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
         <v>84</v>
       </c>
@@ -3835,7 +4150,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
         <v>85</v>
       </c>
@@ -3858,7 +4173,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
         <v>160</v>
       </c>
@@ -3881,7 +4196,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
         <v>86</v>
       </c>
@@ -3904,7 +4219,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
         <v>87</v>
       </c>
@@ -3927,7 +4242,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="14" t="s">
         <v>88</v>
       </c>
@@ -3950,7 +4265,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>
       <c r="B14" s="26"/>
       <c r="C14" s="5"/>
@@ -3959,7 +4274,7 @@
       <c r="F14" s="6"/>
       <c r="G14" s="29"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>
       <c r="B15" s="26"/>
       <c r="C15" s="5"/>
@@ -3968,7 +4283,7 @@
       <c r="F15" s="6"/>
       <c r="G15" s="29"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="13"/>
       <c r="B16" s="26"/>
       <c r="C16" s="5"/>
@@ -3977,7 +4292,7 @@
       <c r="F16" s="6"/>
       <c r="G16" s="29"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="13"/>
       <c r="B17" s="26"/>
       <c r="C17" s="5"/>
@@ -3986,7 +4301,7 @@
       <c r="F17" s="6"/>
       <c r="G17" s="29"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="13"/>
       <c r="B18" s="26"/>
       <c r="C18" s="5"/>
@@ -3995,7 +4310,7 @@
       <c r="F18" s="6"/>
       <c r="G18" s="29"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="13"/>
       <c r="B19" s="26"/>
       <c r="C19" s="5"/>
@@ -4004,7 +4319,7 @@
       <c r="F19" s="6"/>
       <c r="G19" s="29"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="13"/>
       <c r="B20" s="26"/>
       <c r="C20" s="5"/>
@@ -4013,7 +4328,7 @@
       <c r="F20" s="6"/>
       <c r="G20" s="29"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="13"/>
       <c r="B21" s="26"/>
       <c r="C21" s="5"/>
@@ -4022,7 +4337,7 @@
       <c r="F21" s="6"/>
       <c r="G21" s="29"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="13"/>
       <c r="B22" s="26"/>
       <c r="C22" s="5"/>
@@ -4031,7 +4346,7 @@
       <c r="F22" s="6"/>
       <c r="G22" s="29"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="13"/>
       <c r="B23" s="26"/>
       <c r="C23" s="5"/>
@@ -4040,7 +4355,7 @@
       <c r="F23" s="6"/>
       <c r="G23" s="29"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="13"/>
       <c r="B24" s="26"/>
       <c r="C24" s="5"/>
@@ -4049,7 +4364,7 @@
       <c r="F24" s="6"/>
       <c r="G24" s="29"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="13"/>
       <c r="B25" s="26"/>
       <c r="C25" s="5"/>
@@ -4058,7 +4373,7 @@
       <c r="F25" s="6"/>
       <c r="G25" s="29"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="13"/>
       <c r="B26" s="26"/>
       <c r="C26" s="5"/>

--- a/config/tutorial_RC.xlsx
+++ b/config/tutorial_RC.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schir\OneDrive\Studium\34_Github\TherMOS\config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f215465b21b5e6e2/Studium/34_Github/TherMOS/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BDF8ED0-C64B-4A00-BFE4-ABF724044424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{7BDF8ED0-C64B-4A00-BFE4-ABF724044424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50C8FA12-100B-4EA0-83B8-07BA3330596F}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="3" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="1" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
   </bookViews>
   <sheets>
     <sheet name="readme" sheetId="2" r:id="rId1"/>
@@ -1470,6 +1470,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2024,7 +2028,7 @@
         <v>49</v>
       </c>
       <c r="F4" s="11">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="G4" s="29" t="s">
         <v>21</v>
